--- a/artfynd/A 48914-2021 artfynd.xlsx
+++ b/artfynd/A 48914-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48914-2021 artfynd.xlsx
+++ b/artfynd/A 48914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101481361</v>
+        <v>101481355</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valsjöbodarna, Jmt</t>
+          <t>Valsjöboadarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460904.1634655678</v>
+        <v>460866</v>
       </c>
       <c r="R2" t="n">
-        <v>7107041.851543125</v>
+        <v>7107080</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101481367</v>
+        <v>101481345</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460924.6816054439</v>
+        <v>460828</v>
       </c>
       <c r="R3" t="n">
-        <v>7107105.903151513</v>
+        <v>7107056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,24 +847,9 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101481345</v>
+        <v>101481361</v>
       </c>
       <c r="B4" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460828.1204582501</v>
+        <v>460905</v>
       </c>
       <c r="R4" t="n">
-        <v>7107055.934319193</v>
+        <v>7107042</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,19 +948,9 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,42 +978,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101481347</v>
+        <v>101481367</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460828.1204582501</v>
+        <v>460924</v>
       </c>
       <c r="R5" t="n">
-        <v>7107055.934319193</v>
+        <v>7107106</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,24 +1050,14 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Levande gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,122 +1082,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>101481355</v>
-      </c>
-      <c r="B6" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Valsjöboadarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>460865.6517559715</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7107079.522722256</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48914-2021 artfynd.xlsx
+++ b/artfynd/A 48914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101481355</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101481345</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101481361</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,8 +1102,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101481367</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>